--- a/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 5,12</t>
+          <t>-7,43; 4,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 10,87</t>
+          <t>-2,94; 12,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,61</t>
+          <t>-5,13; 6,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 9,57</t>
+          <t>-5,55; 9,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,28; 130,78</t>
+          <t>-71,11; 130,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 126,5</t>
+          <t>-19,81; 146,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,19; 194,45</t>
+          <t>-51,11; 150,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 287,68</t>
+          <t>-57,75; 322,76</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 1,71</t>
+          <t>-7,22; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,83</t>
+          <t>-6,03; 4,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 7,22</t>
+          <t>-2,92; 7,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -1,45</t>
+          <t>-12,15; -1,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 30,76</t>
+          <t>-65,78; 27,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 68,54</t>
+          <t>-47,35; 66,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 103,48</t>
+          <t>-27,53; 110,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,99; -4,66</t>
+          <t>-74,23; -7,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 0,8</t>
+          <t>-12,2; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 6,58</t>
+          <t>-7,24; 6,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,87</t>
+          <t>0,93; 10,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,99</t>
+          <t>-1,8; 6,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 11,7</t>
+          <t>-78,25; 20,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 100,84</t>
+          <t>-59,68; 95,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 500,53</t>
+          <t>-0,92; 573,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 285,98</t>
+          <t>-32,18; 270,72</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,71</t>
+          <t>-1,37; 7,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,53</t>
+          <t>-3,02; 7,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,13</t>
+          <t>-5,12; 4,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 0,06</t>
+          <t>-7,95; 0,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 271,49</t>
+          <t>-25,33; 282,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 243,46</t>
+          <t>-39,0; 238,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,58; 150,96</t>
+          <t>-61,6; 155,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,64; 5,85</t>
+          <t>-72,54; 6,61</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,18</t>
+          <t>-4,12; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,0</t>
+          <t>-1,99; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,42</t>
+          <t>-0,83; 4,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,18</t>
+          <t>-5,03; 0,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 18,0</t>
+          <t>-44,5; 18,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 52,1</t>
+          <t>-18,66; 54,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 81,97</t>
+          <t>-10,93; 86,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 5,05</t>
+          <t>-50,86; 5,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 4,99</t>
+          <t>-7,74; 5,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 12,05</t>
+          <t>-3,98; 11,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 6,54</t>
+          <t>-4,82; 6,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 9,21</t>
+          <t>-6,14; 9,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,11; 130,98</t>
+          <t>-74,64; 131,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 146,3</t>
+          <t>-27,73; 147,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 150,58</t>
+          <t>-50,84; 158,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 322,76</t>
+          <t>-55,65; 312,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,65</t>
+          <t>-6,59; 2,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 4,2</t>
+          <t>-5,9; 4,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 7,05</t>
+          <t>-2,53; 7,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -1,76</t>
+          <t>-12,84; -1,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,78; 27,89</t>
+          <t>-61,4; 34,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 66,01</t>
+          <t>-49,59; 62,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 110,35</t>
+          <t>-24,85; 117,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,23; -7,25</t>
+          <t>-73,99; -9,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 1,17</t>
+          <t>-13,28; 0,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 6,24</t>
+          <t>-7,52; 6,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,41</t>
+          <t>0,92; 10,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 6,69</t>
+          <t>-1,68; 6,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 20,07</t>
+          <t>-79,55; 12,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,68; 95,73</t>
+          <t>-57,41; 98,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 573,13</t>
+          <t>0,76; 511,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 270,72</t>
+          <t>-31,24; 245,11</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,61</t>
+          <t>-1,16; 7,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 7,2</t>
+          <t>-3,64; 7,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 4,92</t>
+          <t>-5,48; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,24</t>
+          <t>-7,86; 0,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 282,21</t>
+          <t>-22,4; 280,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 238,8</t>
+          <t>-48,87; 219,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,6; 155,17</t>
+          <t>-64,13; 158,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 6,61</t>
+          <t>-71,95; 10,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,23</t>
+          <t>-3,99; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,26</t>
+          <t>-1,8; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,66</t>
+          <t>-0,79; 4,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,28</t>
+          <t>-4,63; 0,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 18,72</t>
+          <t>-43,1; 19,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 54,7</t>
+          <t>-17,64; 56,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 86,24</t>
+          <t>-9,91; 88,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 5,59</t>
+          <t>-49,08; 5,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 5,31</t>
+          <t>-7,46; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 11,99</t>
+          <t>-4,16; 10,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 6,77</t>
+          <t>-5,29; 7,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 9,33</t>
+          <t>-4,74; 10,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,64; 131,59</t>
+          <t>-69,28; 130,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 147,64</t>
+          <t>-27,34; 126,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 158,11</t>
+          <t>-54,19; 194,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 312,01</t>
+          <t>-52,46; 320,78</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,83</t>
+          <t>-5,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-51,9%</t>
+          <t>-44,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 2,0</t>
+          <t>-6,95; 1,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,65</t>
+          <t>-6,25; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 7,37</t>
+          <t>-2,95; 7,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; -1,54</t>
+          <t>-10,53; -0,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 34,12</t>
+          <t>-62,61; 30,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 62,18</t>
+          <t>-49,24; 68,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 117,9</t>
+          <t>-28,97; 103,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,99; -9,95</t>
+          <t>-69,31; 2,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 0,46</t>
+          <t>-11,72; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 6,4</t>
+          <t>-6,94; 6,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,09</t>
+          <t>0,18; 9,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 6,84</t>
+          <t>-1,41; 7,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-79,55; 12,7</t>
+          <t>-80,4; 11,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 98,12</t>
+          <t>-56,5; 100,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 511,85</t>
+          <t>-5,7; 500,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 245,11</t>
+          <t>-28,22; 283,16</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,5</t>
+          <t>-3,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,28%</t>
+          <t>-37,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 7,88</t>
+          <t>-1,26; 7,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 7,35</t>
+          <t>-3,51; 7,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 4,42</t>
+          <t>-5,48; 4,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 0,29</t>
+          <t>-7,39; 0,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 280,5</t>
+          <t>-26,71; 271,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 219,53</t>
+          <t>-47,95; 243,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 158,17</t>
+          <t>-66,58; 150,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,95; 10,83</t>
+          <t>-68,12; 13,68</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-26,86%</t>
+          <t>-19,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,22</t>
+          <t>-3,97; 1,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,17</t>
+          <t>-2,11; 4,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,68</t>
+          <t>-0,73; 4,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,45</t>
+          <t>-4,02; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,1; 19,28</t>
+          <t>-42,67; 18,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 56,1</t>
+          <t>-19,37; 52,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 88,26</t>
+          <t>-9,69; 81,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 5,79</t>
+          <t>-43,09; 14,84</t>
         </is>
       </c>
     </row>
